--- a/Penerima Manfaat - Bumil.xlsx
+++ b/Penerima Manfaat - Bumil.xlsx
@@ -638,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -742,7 +742,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -765,7 +765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -788,7 +788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -811,7 +811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -834,7 +834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -857,7 +857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -880,7 +880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>90</v>
       </c>
